--- a/output/review/local-2026-03-21/mchc_review.xlsx
+++ b/output/review/local-2026-03-21/mchc_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mchc" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mchc'!$A$12:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mchc'!$A$12:$L$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,59 +593,65 @@
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SCTID</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>FSN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Complete aggregation</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Quantitative (all numeric)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Quantitative &amp; convertible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Qualitative (ordinal / nominal / presence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Semi-quantitative (test strip)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Panel / order code (no Property)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Use case</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -653,55 +660,60 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>28540-3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>521371010000101</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Entitic mass concentration of hemoglobin in erythrocyte at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>MCHC [Entitic Mass/volume] in Red Blood Cells</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -710,62 +722,67 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>786-4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>613001010000107</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Entitic mass concentration of hemoglobin in erythrocyte at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>MCHC [Entitic Mass/volume] in Red Blood Cells by Automated count</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:K15"/>
+  <autoFilter ref="A12:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>